--- a/China/DATOS_POBLACION.xlsx
+++ b/China/DATOS_POBLACION.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Angelaa\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Angelaa\Documents\GitHub\Actividad-1\China\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1883118B-9A10-4047-9FD9-470BA64C2CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36071288-4318-426B-B116-365A0573BCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99E6F7CB-4D21-43FC-9FA9-420DC92B6817}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8880" xr2:uid="{99E6F7CB-4D21-43FC-9FA9-420DC92B6817}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -141,7 +141,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,6 +153,12 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -237,48 +243,6 @@
   <dxfs count="5">
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -354,6 +318,48 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -368,11 +374,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE2CE22A-784A-4297-BAEC-27D8E1AA0738}" name="Tabla1" displayName="Tabla1" ref="A1:B32" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE2CE22A-784A-4297-BAEC-27D8E1AA0738}" name="Tabla1" displayName="Tabla1" ref="A1:B32" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3" tableBorderDxfId="2">
   <autoFilter ref="A1:B32" xr:uid="{AE2CE22A-784A-4297-BAEC-27D8E1AA0738}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{81D15482-77F8-4E1A-92E2-1AB021D26740}" name="Provincias" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{A1F9EE72-3941-4C10-B954-BD90A2FB4CD4}" name="Población en millones de habitantes" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{81D15482-77F8-4E1A-92E2-1AB021D26740}" name="Provincias" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{A1F9EE72-3941-4C10-B954-BD90A2FB4CD4}" name="Población en millones de habitantes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -715,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3">
-        <v>127.8</v>
+        <v>127800000</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -723,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>100.8</v>
+        <v>100800000</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -731,7 +737,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>97.85</v>
+        <v>97850000</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -739,7 +745,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>85.26</v>
+        <v>85260000</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -747,7 +753,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>83.64</v>
+        <v>83640000</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -755,7 +761,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>73.78</v>
+        <v>73780000</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -763,7 +769,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>66.7</v>
+        <v>66700000</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -771,7 +777,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>65.39</v>
+        <v>65390000</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -779,7 +785,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>61.23</v>
+        <v>61230000</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -787,7 +793,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>58.34</v>
+        <v>58340000</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -795,7 +801,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>50.13</v>
+        <v>50130000</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -803,7 +809,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>46.55</v>
+        <v>46550000</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -811,7 +817,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>45.02</v>
+        <v>45020000</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -819,7 +825,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>41.93</v>
+        <v>41930000</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -827,7 +833,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>41.55</v>
+        <v>41550000</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -835,7 +841,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>39.53</v>
+        <v>39530000</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -843,7 +849,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>38.6</v>
+        <v>38600000</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -851,7 +857,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>34.46</v>
+        <v>34460000</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -859,7 +865,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>31.9</v>
+        <v>31900000</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -867,7 +873,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>30.29</v>
+        <v>30290000</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -875,7 +881,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>26.23</v>
+        <v>26230000</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -883,7 +889,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>24.8</v>
+        <v>24800000</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -891,7 +897,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>24.58</v>
+        <v>24580000</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -899,7 +905,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>23.88</v>
+        <v>23880000</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -907,7 +913,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>23.17</v>
+        <v>23170000</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -915,7 +921,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>21.83</v>
+        <v>21830000</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -923,7 +929,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>13.64</v>
+        <v>13640000</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -931,7 +937,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="3">
-        <v>10.48</v>
+        <v>10480000</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -939,7 +945,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>7.29</v>
+        <v>7290000</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -947,7 +953,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="3">
-        <v>5.93</v>
+        <v>5930000</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -955,7 +961,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="5">
-        <v>3.7</v>
+        <v>3700000</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -963,6 +969,7 @@
       <c r="B33" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
